--- a/程序/附件3 市主城区 10 区域分时段充电负荷.xlsx
+++ b/程序/附件3 市主城区 10 区域分时段充电负荷.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\learn\Desktop\模拟A题\程序\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D3129F-26AC-455E-997D-DEEF5FDDC2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="15825" windowHeight="9150"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作日分时段充电负荷数据" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="28">
   <si>
     <t>区域</t>
   </si>
@@ -108,20 +114,19 @@
     <t/>
   </si>
   <si>
-    <t>充电负荷按某市主流充电桩功率测算，快充桩单枪充电负荷按120kWh / 小时、慢充桩按 7kWh / 小时，混合负荷按实际车次比例折算。</t>
+    <t>average</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>average</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,349 +138,42 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -483,316 +181,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1077,16 +493,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,8 +578,11 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1239,8 +658,12 @@
       <c r="Y2" s="2">
         <v>255</v>
       </c>
+      <c r="Z2">
+        <f>AVERAGE(B2:Y2)</f>
+        <v>800.25</v>
+      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1316,8 +739,12 @@
       <c r="Y3" s="2">
         <v>197</v>
       </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z11" si="0">AVERAGE(B3:Y3)</f>
+        <v>740.29166666666663</v>
+      </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1393,8 +820,12 @@
       <c r="Y4" s="2">
         <v>133</v>
       </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>561.91666666666663</v>
+      </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1470,8 +901,12 @@
       <c r="Y5" s="2">
         <v>308</v>
       </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>828.66666666666663</v>
+      </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1547,8 +982,12 @@
       <c r="Y6" s="2">
         <v>190</v>
       </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>561.04166666666663</v>
+      </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1624,8 +1063,12 @@
       <c r="Y7" s="2">
         <v>241</v>
       </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>765.66666666666663</v>
+      </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1701,8 +1144,12 @@
       <c r="Y8" s="2">
         <v>77</v>
       </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>293.25</v>
+      </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1778,8 +1225,12 @@
       <c r="Y9" s="2">
         <v>69</v>
       </c>
+      <c r="Z9">
+        <f t="shared" si="0"/>
+        <v>396.83333333333331</v>
+      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1855,8 +1306,12 @@
       <c r="Y10" s="2">
         <v>136</v>
       </c>
+      <c r="Z10">
+        <f t="shared" si="0"/>
+        <v>485.08333333333331</v>
+      </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1932,8 +1387,12 @@
       <c r="Y11" s="2">
         <v>123</v>
       </c>
+      <c r="Z11">
+        <f t="shared" si="0"/>
+        <v>397.04166666666669</v>
+      </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +1469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2087,10 +1546,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
       <c r="W14" t="s">
         <v>25</v>
       </c>
@@ -2105,18 +1583,20 @@
   <mergeCells count="1">
     <mergeCell ref="A14:V14"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="Z2" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2192,8 +1672,11 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2269,8 +1752,12 @@
       <c r="Y2" s="2">
         <v>236</v>
       </c>
+      <c r="Z2">
+        <f>AVERAGE(B2:Y2)</f>
+        <v>607.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2346,8 +1833,12 @@
       <c r="Y3" s="2">
         <v>185</v>
       </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z11" si="0">AVERAGE(B3:Y3)</f>
+        <v>556.16666666666663</v>
+      </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2423,8 +1914,12 @@
       <c r="Y4" s="2">
         <v>117</v>
       </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>465.95833333333331</v>
+      </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2500,8 +1995,12 @@
       <c r="Y5" s="2">
         <v>306</v>
       </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>654.625</v>
+      </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2577,8 +2076,12 @@
       <c r="Y6" s="2">
         <v>176</v>
       </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>796.04166666666663</v>
+      </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2654,8 +2157,12 @@
       <c r="Y7" s="2">
         <v>173</v>
       </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>556.25</v>
+      </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2731,8 +2238,12 @@
       <c r="Y8" s="2">
         <v>0</v>
       </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>327.66666666666669</v>
+      </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2808,8 +2319,12 @@
       <c r="Y9" s="2">
         <v>0</v>
       </c>
+      <c r="Z9">
+        <f t="shared" si="0"/>
+        <v>240.625</v>
+      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2885,8 +2400,12 @@
       <c r="Y10" s="2">
         <v>185</v>
       </c>
+      <c r="Z10">
+        <f t="shared" si="0"/>
+        <v>968.375</v>
+      </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2962,9 +2481,13 @@
       <c r="Y11" s="2">
         <v>55</v>
       </c>
+      <c r="Z11">
+        <f t="shared" si="0"/>
+        <v>377.70833333333331</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/程序/附件3 市主城区 10 区域分时段充电负荷.xlsx
+++ b/程序/附件3 市主城区 10 区域分时段充电负荷.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\learn\Desktop\模拟A题\程序\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D3129F-26AC-455E-997D-DEEF5FDDC2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19097DDD-C436-45B0-9FD3-3BF25A0071B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作日分时段充电负荷数据" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="26">
   <si>
     <t>区域</t>
   </si>
@@ -113,20 +113,12 @@
   <si>
     <t/>
   </si>
-  <si>
-    <t>average</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>average</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,14 +136,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -185,15 +169,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -212,6 +193,3778 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$2:$Y$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>983</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>789</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>652</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>668</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1083</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1322</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>972</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>782</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2221</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1744</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1210</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>736</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>255</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$3:$Y$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>439</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>914</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>722</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>618</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1024</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1214</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>918</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>789</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>722</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1395</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2078</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1807</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1596</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1095</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>663</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>434</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>197</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$4:$Y$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>652</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>537</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>466</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>482</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>904</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>734</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>616</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1088</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1534</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1389</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1260</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>853</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>558</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>133</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$5:$Y$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>307</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>549</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>961</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>852</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>728</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>791</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1159</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1397</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1028</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>903</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>843</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1561</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1810</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1627</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1269</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>787</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>549</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>308</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$6:$Y$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>432</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>368</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>483</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>601</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>723</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>914</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>963</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>841</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1085</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1514</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1327</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>969</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>190</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$7:$Y$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>487</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>856</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>793</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>724</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>724</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1267</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>979</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>842</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1453</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1746</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1762</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1568</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1243</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>727</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>241</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$8:$Y$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>319</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>429</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>377</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>727</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>602</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>483</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>377</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>77</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$9:$Y$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>794</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>607</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>431</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>377</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>798</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>551</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>436</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>316</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$10:$Y$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>319</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>427</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>549</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>661</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>788</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>727</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>858</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>908</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>781</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>971</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1218</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1090</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>783</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>487</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>316</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>136</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>工作日分时段充电负荷数据!$B$11:$Y$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>429</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>369</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>423</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>616</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>736</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>543</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>431</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>677</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>908</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>784</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>548</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>123</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-077C-4ABA-BC3C-993063432A1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="173407888"/>
+        <c:axId val="153973200"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="173407888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="153973200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="153973200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="173407888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$2:$Y$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>474</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>594</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>727</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>953</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1096</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1182</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1304</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1212</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1089</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>607</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>236</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$3:$Y$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>411</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>537</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>657</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>793</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1035</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1132</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>893</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>787</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>678</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>533</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>414</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>311</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$4:$Y$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>434</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>529</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>767</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1159</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>772</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>652</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>554</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>117</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$5:$Y$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>357</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>649</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>788</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1029</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1253</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1396</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1266</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1131</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1027</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>919</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>559</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>433</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>306</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$6:$Y$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>478</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>722</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1087</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1487</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1694</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1808</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1725</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1616</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1490</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1331</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1187</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1093</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>728</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>551</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>176</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$7:$Y$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>424</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>668</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>772</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>906</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1267</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1155</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1023</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>896</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>547</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>427</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>173</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$8:$Y$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>422</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>547</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>794</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>894</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>729</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>589</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>351</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$9:$Y$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>367</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>478</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>611</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>538</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>473</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>409</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>356</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>304</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>364</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>471</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$10:$Y$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>419</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>716</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1084</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1915</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2095</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2285</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2156</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1806</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1549</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1312</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1091</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>888</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>528</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>352</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'周末充电负荷数据（修改后）'!$B$11:$Y$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>474</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>603</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>716</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>952</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>902</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>772</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>669</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>546</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>426</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>303</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-FC89-401F-B50A-F5F902F23356}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="171751232"/>
+        <c:axId val="153967920"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="171751232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="153967920"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="153967920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="171751232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>130175</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{689194A0-1D06-9CB2-5900-0E3E6BF4C85E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>130175</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E407EE-5778-08E3-C40B-7F581FC7D53C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,10 +4252,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,11 +4331,8 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -658,12 +4408,8 @@
       <c r="Y2" s="2">
         <v>255</v>
       </c>
-      <c r="Z2">
-        <f>AVERAGE(B2:Y2)</f>
-        <v>800.25</v>
-      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -739,12 +4485,8 @@
       <c r="Y3" s="2">
         <v>197</v>
       </c>
-      <c r="Z3">
-        <f t="shared" ref="Z3:Z11" si="0">AVERAGE(B3:Y3)</f>
-        <v>740.29166666666663</v>
-      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -820,12 +4562,8 @@
       <c r="Y4" s="2">
         <v>133</v>
       </c>
-      <c r="Z4">
-        <f t="shared" si="0"/>
-        <v>561.91666666666663</v>
-      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -901,12 +4639,8 @@
       <c r="Y5" s="2">
         <v>308</v>
       </c>
-      <c r="Z5">
-        <f t="shared" si="0"/>
-        <v>828.66666666666663</v>
-      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -982,12 +4716,8 @@
       <c r="Y6" s="2">
         <v>190</v>
       </c>
-      <c r="Z6">
-        <f t="shared" si="0"/>
-        <v>561.04166666666663</v>
-      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1063,12 +4793,8 @@
       <c r="Y7" s="2">
         <v>241</v>
       </c>
-      <c r="Z7">
-        <f t="shared" si="0"/>
-        <v>765.66666666666663</v>
-      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1144,12 +4870,8 @@
       <c r="Y8" s="2">
         <v>77</v>
       </c>
-      <c r="Z8">
-        <f t="shared" si="0"/>
-        <v>293.25</v>
-      </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1225,12 +4947,8 @@
       <c r="Y9" s="2">
         <v>69</v>
       </c>
-      <c r="Z9">
-        <f t="shared" si="0"/>
-        <v>396.83333333333331</v>
-      </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1306,12 +5024,8 @@
       <c r="Y10" s="2">
         <v>136</v>
       </c>
-      <c r="Z10">
-        <f t="shared" si="0"/>
-        <v>485.08333333333331</v>
-      </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1387,12 +5101,8 @@
       <c r="Y11" s="2">
         <v>123</v>
       </c>
-      <c r="Z11">
-        <f t="shared" si="0"/>
-        <v>397.04166666666669</v>
-      </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1469,7 +5179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1546,29 +5256,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
       <c r="W14" t="s">
         <v>25</v>
       </c>
@@ -1585,18 +5295,16 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError sqref="Z2" formulaRange="1"/>
-  </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1672,11 +5380,8 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1752,12 +5457,8 @@
       <c r="Y2" s="2">
         <v>236</v>
       </c>
-      <c r="Z2">
-        <f>AVERAGE(B2:Y2)</f>
-        <v>607.5</v>
-      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1833,12 +5534,8 @@
       <c r="Y3" s="2">
         <v>185</v>
       </c>
-      <c r="Z3">
-        <f t="shared" ref="Z3:Z11" si="0">AVERAGE(B3:Y3)</f>
-        <v>556.16666666666663</v>
-      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1914,12 +5611,8 @@
       <c r="Y4" s="2">
         <v>117</v>
       </c>
-      <c r="Z4">
-        <f t="shared" si="0"/>
-        <v>465.95833333333331</v>
-      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1995,12 +5688,8 @@
       <c r="Y5" s="2">
         <v>306</v>
       </c>
-      <c r="Z5">
-        <f t="shared" si="0"/>
-        <v>654.625</v>
-      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2076,12 +5765,8 @@
       <c r="Y6" s="2">
         <v>176</v>
       </c>
-      <c r="Z6">
-        <f t="shared" si="0"/>
-        <v>796.04166666666663</v>
-      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2157,12 +5842,8 @@
       <c r="Y7" s="2">
         <v>173</v>
       </c>
-      <c r="Z7">
-        <f t="shared" si="0"/>
-        <v>556.25</v>
-      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2238,12 +5919,8 @@
       <c r="Y8" s="2">
         <v>0</v>
       </c>
-      <c r="Z8">
-        <f t="shared" si="0"/>
-        <v>327.66666666666669</v>
-      </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2319,12 +5996,8 @@
       <c r="Y9" s="2">
         <v>0</v>
       </c>
-      <c r="Z9">
-        <f t="shared" si="0"/>
-        <v>240.625</v>
-      </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2400,12 +6073,8 @@
       <c r="Y10" s="2">
         <v>185</v>
       </c>
-      <c r="Z10">
-        <f t="shared" si="0"/>
-        <v>968.375</v>
-      </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2481,13 +6150,10 @@
       <c r="Y11" s="2">
         <v>55</v>
       </c>
-      <c r="Z11">
-        <f t="shared" si="0"/>
-        <v>377.70833333333331</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>